--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:48+00:00</t>
+    <t>2024-04-09T07:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
+++ b/main/ig/ValueSet-VS-TRE-R286-TypeFermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
